--- a/artfynd/A 11065-2026 artfynd.xlsx
+++ b/artfynd/A 11065-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101955883</v>
+        <v>131584476</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>1131</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Asphättemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Nyholmiella gymnostoma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Bruch ex Brid.) Holmen &amp; Warncke</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåvetakvarn 150m no, Srm</t>
+          <t>Kåvetakvarn 200m no, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609473.5191960977</v>
+        <v>609371</v>
       </c>
       <c r="R2" t="n">
-        <v>6551047.688817947</v>
+        <v>6551132</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsväg</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,12 +785,7 @@
         <v>101955928</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609473.5191960977</v>
+        <v>609473</v>
       </c>
       <c r="R3" t="n">
-        <v>6551047.688817947</v>
+        <v>6551048</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,19 +854,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,12 +892,7 @@
         <v>102048400</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609473.5191960977</v>
+        <v>609473</v>
       </c>
       <c r="R4" t="n">
-        <v>6551047.688817947</v>
+        <v>6551048</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +961,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,6 +993,438 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122401705</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kåvetakvarn 250m NV, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>609248</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6551168</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101955883</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kåvetakvarn 150m no, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>609473</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6551048</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102048110</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kåvetakvarn 150m no, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609473</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6551048</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122401690</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kåvetakvarn 250m NV, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609248</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6551168</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11065-2026 artfynd.xlsx
+++ b/artfynd/A 11065-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101955928</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102048400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122401705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101955883</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102048110</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,8 +1460,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122401690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>